--- a/jogos_2025-12-11.xlsx
+++ b/jogos_2025-12-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2025-12-11.xlsx
+++ b/jogos_2025-12-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2025-12-11.xlsx
+++ b/jogos_2025-12-11.xlsx
@@ -662,28 +662,28 @@
         <v>1.88</v>
       </c>
       <c r="M2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>2.7</v>
+        <v>3.47</v>
       </c>
       <c r="O2" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="P2" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.09</v>
+        <v>3.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
         <v>3.13</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="U2" t="n">
         <v>1.5</v>
@@ -692,7 +692,7 @@
         <v>5.75</v>
       </c>
       <c r="W2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
         <v>1.04</v>
@@ -701,31 +701,31 @@
         <v>1.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AC2" t="n">
         <v>2.75</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46002.66666666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2025-12-11.xlsx
+++ b/jogos_2025-12-11.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>3.47</v>
+        <v>3.55</v>
       </c>
       <c r="O2" t="n">
         <v>2.45</v>
@@ -704,10 +704,10 @@
         <v>4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AC2" t="n">
         <v>2.75</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2025-12-11.xlsx
+++ b/jogos_2025-12-11.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="M2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>3.55</v>
+        <v>3.47</v>
       </c>
       <c r="O2" t="n">
         <v>2.45</v>
@@ -704,10 +704,10 @@
         <v>4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AC2" t="n">
         <v>2.75</v>

--- a/jogos_2025-12-11.xlsx
+++ b/jogos_2025-12-11.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="M2" t="n">
         <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>3.47</v>
+        <v>3.6</v>
       </c>
       <c r="O2" t="n">
         <v>2.45</v>
@@ -704,10 +704,10 @@
         <v>4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AC2" t="n">
         <v>2.75</v>

--- a/jogos_2025-12-11.xlsx
+++ b/jogos_2025-12-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>

--- a/jogos_2025-12-11.xlsx
+++ b/jogos_2025-12-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46002.70833333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.2</v>
+        <v>4.12</v>
       </c>
       <c r="M5" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="N5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB5" t="n">
         <v>1.95</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46002.8125</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N6" t="n">
         <v>2.5</v>
       </c>
-      <c r="M6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.7</v>
-      </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46002.89583333334</v>

--- a/jogos_2025-12-11.xlsx
+++ b/jogos_2025-12-11.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="M2" t="n">
         <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="O2" t="n">
         <v>2.45</v>
@@ -704,10 +704,10 @@
         <v>4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AC2" t="n">
         <v>2.75</v>

--- a/jogos_2025-12-11.xlsx
+++ b/jogos_2025-12-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.69</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
-        <v>3.9</v>
+        <v>4.04</v>
       </c>
       <c r="N3" t="n">
-        <v>4.13</v>
+        <v>7.13</v>
       </c>
       <c r="O3" t="n">
-        <v>2.22</v>
+        <v>1.98</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.49</v>
+        <v>7.85</v>
       </c>
       <c r="R3" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="T3" t="n">
-        <v>2.35</v>
+        <v>2.72</v>
       </c>
       <c r="U3" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="V3" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="W3" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.85</v>
+        <v>3.28</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.07</v>
+        <v>2.59</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46002.70833333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46002.70833333334</v>
@@ -1016,16 +1016,16 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.12</v>
+        <v>3.9</v>
       </c>
       <c r="M5" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="O5" t="n">
-        <v>4.81</v>
+        <v>4.5</v>
       </c>
       <c r="P5" t="n">
         <v>2.17</v>
@@ -1034,55 +1034,55 @@
         <v>2.27</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="T5" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
         <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
         <v>1.95</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AF5" t="n">
         <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.21</v>
+        <v>1.89</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46002.8125</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O6" t="n">
         <v>3.3</v>
@@ -1159,7 +1159,7 @@
         <v>2.53</v>
       </c>
       <c r="T6" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
         <v>1.3</v>
@@ -1171,37 +1171,37 @@
         <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.95</v>
+        <v>3.78</v>
       </c>
       <c r="AD6" t="n">
         <v>1.22</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
         <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46002.89583333334</v>

--- a/jogos_2025-12-11.xlsx
+++ b/jogos_2025-12-11.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="M2" t="n">
         <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="O2" t="n">
         <v>2.45</v>
@@ -704,10 +704,10 @@
         <v>4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AC2" t="n">
         <v>2.75</v>

--- a/jogos_2025-12-11.xlsx
+++ b/jogos_2025-12-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="M3" t="n">
-        <v>4.04</v>
+        <v>3.9</v>
       </c>
       <c r="N3" t="n">
-        <v>7.13</v>
+        <v>4.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="P3" t="n">
-        <v>2.09</v>
+        <v>2.48</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.85</v>
+        <v>5.1</v>
       </c>
       <c r="R3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1.36</v>
       </c>
-      <c r="S3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE3" t="n">
-        <v>2.15</v>
+        <v>1.74</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.59</v>
+        <v>2.2</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46002.70833333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9</v>
+        <v>4.04</v>
       </c>
       <c r="N4" t="n">
-        <v>4.8</v>
+        <v>7.13</v>
       </c>
       <c r="O4" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="P4" t="n">
-        <v>2.48</v>
+        <v>2.09</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.1</v>
+        <v>7.85</v>
       </c>
       <c r="R4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.25</v>
       </c>
-      <c r="S4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T4" t="n">
+      <c r="AE4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH4" t="n">
         <v>2.59</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>2.2</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46002.70833333334</v>

--- a/jogos_2025-12-11.xlsx
+++ b/jogos_2025-12-11.xlsx
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="M3" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="O3" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="P3" t="n">
         <v>2.48</v>
@@ -802,49 +802,49 @@
         <v>3.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="U3" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
         <v>1.04</v>
       </c>
       <c r="Y3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH3" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46002.70833333334</v>
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>4.04</v>
+        <v>3.65</v>
       </c>
       <c r="N4" t="n">
-        <v>7.13</v>
+        <v>6.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="P4" t="n">
-        <v>2.09</v>
+        <v>2.27</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.85</v>
+        <v>7.75</v>
       </c>
       <c r="R4" t="n">
         <v>1.36</v>
@@ -936,28 +936,28 @@
         <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG4" t="n">
         <v>1.17</v>
@@ -1016,37 +1016,37 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N5" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="O5" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="P5" t="n">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="T5" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="U5" t="n">
         <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="W5" t="n">
         <v>1.11</v>
@@ -1055,10 +1055,10 @@
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA5" t="n">
         <v>1.75</v>
@@ -1067,22 +1067,22 @@
         <v>1.95</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.89</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46002.8125</v>
@@ -1138,70 +1138,70 @@
         <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="U6" t="n">
         <v>1.3</v>
       </c>
       <c r="V6" t="n">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.78</v>
+        <v>4.05</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46002.89583333334</v>

--- a/jogos_2025-12-11.xlsx
+++ b/jogos_2025-12-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N3" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="O3" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="P3" t="n">
-        <v>2.48</v>
+        <v>2.27</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.1</v>
+        <v>7.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V3" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="W3" t="n">
         <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.3</v>
+        <v>2.59</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46002.70833333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="M4" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N4" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="P4" t="n">
-        <v>2.27</v>
+        <v>2.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.75</v>
+        <v>5.1</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="W4" t="n">
         <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46002.70833333334</v>
@@ -975,7 +975,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1085,7 +1085,7 @@
         <v>1.15</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>46002.8125</v>
+        <v>46002.79166666666</v>
       </c>
     </row>
     <row r="6">

--- a/jogos_2025-12-11.xlsx
+++ b/jogos_2025-12-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="M3" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.27</v>
+        <v>2.48</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.75</v>
+        <v>5.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="U3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="W3" t="n">
         <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46002.70833333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N4" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="O4" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="P4" t="n">
-        <v>2.48</v>
+        <v>2.27</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.1</v>
+        <v>7.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V4" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="W4" t="n">
         <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.3</v>
+        <v>2.59</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46002.70833333334</v>

--- a/jogos_2025-12-11.xlsx
+++ b/jogos_2025-12-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N3" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="O3" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="P3" t="n">
-        <v>2.48</v>
+        <v>2.27</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.1</v>
+        <v>7.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V3" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="W3" t="n">
         <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.3</v>
+        <v>2.59</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46002.70833333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="M4" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N4" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="P4" t="n">
-        <v>2.27</v>
+        <v>2.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.75</v>
+        <v>5.1</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="W4" t="n">
         <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46002.70833333334</v>

--- a/jogos_2025-12-11.xlsx
+++ b/jogos_2025-12-11.xlsx
@@ -787,40 +787,40 @@
         <v>6.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.27</v>
+        <v>2.09</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.75</v>
+        <v>7.55</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="T3" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="U3" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="V3" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="AA3" t="n">
         <v>2</v>
@@ -829,22 +829,22 @@
         <v>1.72</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE3" t="n">
         <v>2.17</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AG3" t="n">
         <v>1.17</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46002.70833333334</v>
@@ -897,28 +897,28 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="N4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O4" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="P4" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="T4" t="n">
         <v>2.6</v>
@@ -936,34 +936,34 @@
         <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
         <v>3.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
         <v>1.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46002.70833333334</v>
@@ -1025,25 +1025,25 @@
         <v>1.73</v>
       </c>
       <c r="O5" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S5" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="T5" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V5" t="n">
         <v>5.7</v>
@@ -1055,10 +1055,10 @@
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AA5" t="n">
         <v>1.75</v>
@@ -1067,13 +1067,13 @@
         <v>1.95</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AD5" t="n">
         <v>1.37</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AF5" t="n">
         <v>1.95</v>
@@ -1144,22 +1144,22 @@
         <v>2.7</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="P6" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
         <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="U6" t="n">
         <v>1.3</v>
@@ -1174,10 +1174,10 @@
         <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AA6" t="n">
         <v>2.12</v>
@@ -1186,19 +1186,19 @@
         <v>1.64</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AD6" t="n">
         <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH6" t="n">
         <v>1.36</v>

--- a/jogos_2025-12-11.xlsx
+++ b/jogos_2025-12-11.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="M2" t="n">
         <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="O2" t="n">
         <v>2.45</v>
@@ -704,10 +704,10 @@
         <v>4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AC2" t="n">
         <v>2.75</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="M3" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="N3" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="P3" t="n">
-        <v>2.09</v>
+        <v>2.38</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.55</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S3" t="n">
         <v>2.8</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="U3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V3" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.04</v>
+        <v>3.48</v>
       </c>
       <c r="AA3" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AD3" t="n">
         <v>1.28</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.17</v>
+        <v>1.78</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.58</v>
+        <v>1.86</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.55</v>
+        <v>2.03</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46002.70833333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="M4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>5.6</v>
+        <v>7.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="P4" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>2.99</v>
+        <v>2.59</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
         <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.7</v>
+        <v>2.92</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.9</v>
+        <v>3.58</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46002.70833333334</v>
@@ -1016,40 +1016,40 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="M5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N5" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="O5" t="n">
         <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="R5" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="T5" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
         <v>1.04</v>
@@ -1058,16 +1058,16 @@
         <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="AD5" t="n">
         <v>1.37</v>
@@ -1076,7 +1076,7 @@
         <v>1.73</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
         <v>1.25</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="N6" t="n">
         <v>2.5</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3.25</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O6" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.9</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="T6" t="n">
-        <v>3.28</v>
+        <v>4.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="V6" t="n">
-        <v>9.5</v>
+        <v>12</v>
       </c>
       <c r="W6" t="n">
         <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AB6" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z6" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AC6" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.77</v>
+        <v>1.51</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46002.89583333334</v>

--- a/jogos_2025-12-11.xlsx
+++ b/jogos_2025-12-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="M3" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>4.5</v>
+        <v>7.25</v>
       </c>
       <c r="O3" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="P3" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="R3" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="T3" t="n">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="U3" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.48</v>
+        <v>2.92</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.86</v>
+        <v>1.58</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46002.70833333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="N4" t="n">
-        <v>7.25</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.92</v>
+        <v>3.48</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.08</v>
+        <v>1.78</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.58</v>
+        <v>1.86</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46002.70833333334</v>

--- a/jogos_2025-12-11.xlsx
+++ b/jogos_2025-12-11.xlsx
@@ -642,20 +642,20 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -761,20 +761,20 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -880,20 +880,20 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1016,49 +1016,49 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N5" t="n">
         <v>1.55</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="T5" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="AA5" t="n">
         <v>1.76</v>
@@ -1067,22 +1067,22 @@
         <v>1.96</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46002.79166666666</v>
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.04</v>
+        <v>2.78</v>
       </c>
       <c r="M6" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="N6" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="R6" t="n">
         <v>1.55</v>
@@ -1159,49 +1159,49 @@
         <v>2.15</v>
       </c>
       <c r="T6" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="V6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="Z6" t="n">
         <v>2.12</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="AB6" t="n">
         <v>1.38</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AE6" t="n">
         <v>2.3</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG6" t="n">
         <v>1.44</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46002.89583333334</v>
